--- a/artfynd/A 12271-2024 artfynd.xlsx
+++ b/artfynd/A 12271-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104023147</v>
+        <v>104023109</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baptisttjärnen, Jmt</t>
+          <t>Hundtjärnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551003.6037271762</v>
+        <v>550943</v>
       </c>
       <c r="R2" t="n">
-        <v>6995928.831500758</v>
+        <v>6996333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -799,16 +789,11 @@
         <v>104023128</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551093.9190571514</v>
+        <v>551094</v>
       </c>
       <c r="R3" t="n">
-        <v>6995984.621288707</v>
+        <v>6995985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,6 +890,122 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104023147</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Baptisttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>551004</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6995929</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 12271-2024 artfynd.xlsx
+++ b/artfynd/A 12271-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023109</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,8 +1025,18 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023147</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>